--- a/Data/Regression Evidence 2025/Workday_NewHire_Romania_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Romania_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{B9113D06-D0DD-4F78-894E-ACBB3F606FCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{A0005250-476B-4352-83CE-5FA56B7A03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,10 +274,10 @@
     <t>Romania</t>
   </si>
   <si>
-    <t>Amiya</t>
-  </si>
-  <si>
-    <t>Crist</t>
+    <t>Juana</t>
+  </si>
+  <si>
+    <t>Reynolds</t>
   </si>
   <si>
     <t>Mobile</t>
@@ -367,7 +367,7 @@
     <t>Personal Numeric Code (CNP)</t>
   </si>
   <si>
-    <t>1630206286971</t>
+    <t>1630206286975</t>
   </si>
   <si>
     <t>01/01/2000</t>
@@ -421,408 +421,411 @@
     <t>Test2</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Bradly Borer' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
+    <t xml:space="preserve">Test failed for 'Shyanne Senger' Employee:{}TimeoutError: locator.click: Timeout 30000ms exceeded.
 Call log:
   [2m- waiting for getByLabel('My Tasks Items')[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-z" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
 [2m  - attempting click action[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #1[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #2[22m
 [2m  -   waiting 20ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #3[22m
 [2m  -   waiting 100ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #4[22m
 [2m  -   waiting 100ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #5[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #6[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #7[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #8[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #9[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #10[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #11[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #12[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #13[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #14[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #15[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #16[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #17[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #18[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #19[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #20[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #21[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #22[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #23[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #24[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #25[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #26[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #27[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #28[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #29[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #30[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #31[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #32[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #33[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #34[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #35[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #36[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #37[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #38[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #39[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #40[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #41[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #42[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #43[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #44[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #45[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #46[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #47[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #48[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #49[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #50[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #51[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #52[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #53[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #54[22m
 [2m  -   waiting 500ms[22m
 [2m  -   waiting for element to be visible, enabled and stable[22m
 [2m  -   element is visible, enabled and stable[22m
 [2m  -   scrolling into view if needed[22m
 [2m  -   done scrolling[22m
-[2m  -   &lt;div class="WGIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  -   &lt;div class="WFIP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
 [2m  - retrying click action, attempt #55[22m
 [2m  -   waiting 500ms[22m
 </t>
   </si>
   <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>880 Store Management (Suvug Rozery (10629083))</t>
   </si>
   <si>
-    <t>Bradly</t>
-  </si>
-  <si>
-    <t>Borer</t>
-  </si>
-  <si>
-    <t>Auto 58592348</t>
+    <t>Shyanne</t>
+  </si>
+  <si>
+    <t>Senger</t>
+  </si>
+  <si>
+    <t>Auto 40617717</t>
   </si>
   <si>
     <t>Store Manager_NEW</t>
@@ -837,13 +840,10 @@
     <t>251 Management Retail</t>
   </si>
   <si>
-    <t>1321228095901</t>
-  </si>
-  <si>
-    <t>10700289</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t>1321228095907</t>
+  </si>
+  <si>
+    <t>10700477</t>
   </si>
 </sst>
 </file>
@@ -1726,10 +1726,10 @@
         <v>77</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>79</v>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="K2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="L2" s="14" t="s">
         <v>80</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="W2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="X2" s="16" t="s">
         <v>91</v>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AT2" s="17" t="str">
         <f t="shared" ref="AT2:AT3" ca="1" si="0">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="AU2" s="14" t="s">
         <v>99</v>
@@ -1877,11 +1877,11 @@
       </c>
       <c r="AY2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="AZ2" s="17">
         <f ca="1">TODAY()-100</f>
-        <v>45756</v>
+        <v>45777</v>
       </c>
       <c r="BA2" s="26" t="s">
         <v>99</v>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="BI2" s="32">
         <f t="array" aca="1" ref="BI2:BI3" ca="1">_xlfn.RANDARRAY(2,1,123456,999999,TRUE)</f>
-        <v>227322</v>
+        <v>664117</v>
       </c>
       <c r="BJ2" s="19" t="s">
         <v>113</v>
@@ -1986,16 +1986,16 @@
         <v>78</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E3" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H3" s="16">
         <v>720527700</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="K3" s="36" t="str">
         <f t="shared" ref="K3" ca="1" si="1">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="L3" s="33" t="s">
         <v>80</v>
@@ -2045,22 +2045,22 @@
       </c>
       <c r="W3" s="36" t="str">
         <f t="shared" ref="W3" ca="1" si="2">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="X3" s="16" t="s">
         <v>91</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Z3" s="23" t="s">
         <v>93</v>
       </c>
       <c r="AA3" s="23" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AB3" s="38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AC3" s="21">
         <v>880</v>
@@ -2084,10 +2084,10 @@
         <v>100</v>
       </c>
       <c r="AJ3" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK3" s="41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AL3" s="16" t="s">
         <v>103</v>
@@ -2115,7 +2115,7 @@
       </c>
       <c r="AT3" s="17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="AU3" s="14" t="s">
         <v>99</v>
@@ -2131,11 +2131,11 @@
       </c>
       <c r="AY3" s="36" t="str">
         <f t="shared" ref="AY3:AZ3" ca="1" si="3">TEXT(TODAY()-100,"DD/MM/YYYY")</f>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="AZ3" s="36" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>09/04/2025</v>
+        <v>30/04/2025</v>
       </c>
       <c r="BA3" s="39" t="str">
         <f>AH3</f>
@@ -2148,7 +2148,7 @@
         <v>111</v>
       </c>
       <c r="BD3" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BE3" s="19" t="s">
         <v>113</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="BI3" s="32">
         <f ca="1"/>
-        <v>133981</v>
+        <v>447695</v>
       </c>
       <c r="BJ3" s="19" t="s">
         <v>113</v>
